--- a/data/trans_orig/P1430-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1430-Provincia-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de cirrosis en 2012</t>
+          <t>Población con diagnóstico de cirrosis en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>985</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8504</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>991</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8495</t>
+          <t>8259</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>292739</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>294738</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>278741</t>
+          <t>278867</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>286259</t>
+          <t>286260</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>573488</t>
+          <t>573724</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>580995</t>
+          <t>580992</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9197</t>
+          <t>9207</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8159</t>
+          <t>8435</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2138</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12674</t>
+          <t>12219</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>496330</t>
+          <t>496320</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>515606</t>
+          <t>515330</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1016618</t>
+          <t>1017073</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1027154</t>
+          <t>1027267</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4695</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7308</t>
+          <t>7459</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>936</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8330</t>
+          <t>8946</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>319351</t>
+          <t>319834</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>333712</t>
+          <t>333561</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>656736</t>
+          <t>656120</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>664134</t>
+          <t>664130</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7613</t>
+          <t>7394</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2138</t>
+          <t>2140</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13224</t>
+          <t>12040</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3269</t>
+          <t>3238</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14445</t>
+          <t>14223</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>366369</t>
+          <t>366588</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>375727</t>
+          <t>376911</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>386813</t>
+          <t>386811</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>748488</t>
+          <t>748710</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>759664</t>
+          <t>759695</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,58%</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6819</t>
+          <t>5712</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,62 +2138,62 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>1146</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>1978</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>5713</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1146</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>5231</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>205799</t>
+          <t>206906</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>217613</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>219591</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>426978</t>
+          <t>426496</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6867</t>
+          <t>7163</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4971</t>
+          <t>5015</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>994</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8209</t>
+          <t>8450</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>267114</t>
+          <t>266818</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>273125</t>
+          <t>273081</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>543868</t>
+          <t>543627</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>551092</t>
+          <t>551083</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4055</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19759</t>
+          <t>18931</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>1873</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10055</t>
+          <t>10077</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6284</t>
+          <t>7170</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24429</t>
+          <t>25007</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>643029</t>
+          <t>643857</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>658733</t>
+          <t>658714</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>683798</t>
+          <t>683776</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>692856</t>
+          <t>691980</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1332212</t>
+          <t>1331634</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1350357</t>
+          <t>1349471</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11652</t>
+          <t>11554</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10787</t>
+          <t>10538</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>5237</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17706</t>
+          <t>17796</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>767446</t>
+          <t>767544</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>777035</t>
+          <t>777055</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>811791</t>
+          <t>812040</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>821550</t>
+          <t>821549</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1583970</t>
+          <t>1583880</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1596428</t>
+          <t>1596439</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>15804</t>
+          <t>15559</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>38260</t>
+          <t>37453</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3490,12 +3490,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>13852</t>
+          <t>13881</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>33525</t>
+          <t>32609</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>33743</t>
+          <t>33844</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>63517</t>
+          <t>63330</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3388519</t>
+          <t>3389326</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3410975</t>
+          <t>3411220</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3603,12 +3603,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3521573</t>
+          <t>3522489</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3541246</t>
+          <t>3541217</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6918360</t>
+          <t>6918547</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6948134</t>
+          <t>6948033</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de cirrosis en 2016</t>
+          <t>Población con diagnóstico de cirrosis en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11486</t>
+          <t>13498</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>4618</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2530</t>
+          <t>1879</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14331</t>
+          <t>12953</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>282275</t>
+          <t>280263</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>292497</t>
+          <t>292504</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>283423</t>
+          <t>284085</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>568133</t>
+          <t>569511</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>579934</t>
+          <t>580585</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,68%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8737</t>
+          <t>8658</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7778</t>
+          <t>8055</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12357</t>
+          <t>11682</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>493838</t>
+          <t>493917</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>501556</t>
+          <t>501558</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>515306</t>
+          <t>515029</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1013302</t>
+          <t>1013977</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1023562</t>
+          <t>1023645</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3875</t>
+          <t>4651</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4420</t>
+          <t>4477</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6356</t>
+          <t>5450</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>314690</t>
+          <t>313914</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>331889</t>
+          <t>331832</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>648518</t>
+          <t>649424</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5966</t>
+          <t>6943</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11802</t>
+          <t>10432</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>984</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12394</t>
+          <t>13374</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>363998</t>
+          <t>363021</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>375481</t>
+          <t>376851</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>744853</t>
+          <t>743873</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>756270</t>
+          <t>756263</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5426,82 +5426,82 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1956</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1903</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5999</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>1956</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5907</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1956</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6842</t>
+          <t>6824</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>209318</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>211221</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5554,42 +5554,42 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>216631</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>212588</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>218587</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
           <t>99,1%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>216631</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>212680</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>218587</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,1%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>422966</t>
+          <t>422984</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>791</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8282</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5809,7 +5809,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5889</t>
+          <t>4502</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>999</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9003</t>
+          <t>9687</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>254841</t>
+          <t>255087</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>262335</t>
+          <t>262332</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>267226</t>
+          <t>268613</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>527235</t>
+          <t>526551</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>535209</t>
+          <t>535239</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5967,7 +5967,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10889</t>
+          <t>11588</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5538</t>
+          <t>6853</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1126</t>
+          <t>1123</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13406</t>
+          <t>11850</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -6225,7 +6225,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>645669</t>
+          <t>644970</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -6260,7 +6260,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>685756</t>
+          <t>684441</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1334446</t>
+          <t>1336002</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1346726</t>
+          <t>1346729</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3637</t>
+          <t>3046</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15764</t>
+          <t>15978</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>996</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8484</t>
+          <t>8353</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5116</t>
+          <t>5234</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19826</t>
+          <t>19017</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -6568,12 +6568,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>762819</t>
+          <t>762605</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>774946</t>
+          <t>775537</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>817683</t>
+          <t>817814</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>825169</t>
+          <t>825171</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6618,7 +6618,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1584924</t>
+          <t>1585733</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1599634</t>
+          <t>1599516</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,67%</t>
         </is>
       </c>
     </row>
@@ -6798,12 +6798,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>14996</t>
+          <t>15005</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>36530</t>
+          <t>36242</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6818,7 +6818,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7269</t>
+          <t>7265</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>25495</t>
+          <t>23697</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6868,12 +6868,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>25979</t>
+          <t>27544</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>53836</t>
+          <t>53748</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -6911,12 +6911,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3357820</t>
+          <t>3358108</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3379354</t>
+          <t>3379345</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3519047</t>
+          <t>3520845</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3537273</t>
+          <t>3537277</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6885056</t>
+          <t>6885144</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6912913</t>
+          <t>6911348</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1430-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1430-Provincia-trans_orig.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>983</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8378</t>
+          <t>9036</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>989</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8259</t>
+          <t>8340</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>278867</t>
+          <t>278209</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>286260</t>
+          <t>286262</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>573724</t>
+          <t>573643</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>580992</t>
+          <t>580994</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9207</t>
+          <t>9631</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8435</t>
+          <t>7413</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2160</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12219</t>
+          <t>12412</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>496320</t>
+          <t>495896</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>504491</t>
+          <t>504486</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>515330</t>
+          <t>516352</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1017073</t>
+          <t>1016880</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1027267</t>
+          <t>1027132</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4212</t>
+          <t>5421</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7459</t>
+          <t>7664</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>935</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8946</t>
+          <t>8318</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>319834</t>
+          <t>318625</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>333561</t>
+          <t>333356</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>656120</t>
+          <t>656748</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>664130</t>
+          <t>664131</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7394</t>
+          <t>6453</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2140</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12040</t>
+          <t>12084</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3238</t>
+          <t>3246</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14223</t>
+          <t>14928</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>366588</t>
+          <t>367529</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>376911</t>
+          <t>376867</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>386811</t>
+          <t>386801</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>748710</t>
+          <t>748005</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>759695</t>
+          <t>759687</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5712</t>
+          <t>5792</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5713</t>
+          <t>6423</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>206906</t>
+          <t>206826</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>426496</t>
+          <t>425786</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7163</t>
+          <t>6982</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5015</t>
+          <t>5945</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>986</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8450</t>
+          <t>8174</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>266818</t>
+          <t>266999</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>273081</t>
+          <t>272151</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>543627</t>
+          <t>543903</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>551083</t>
+          <t>551091</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>4040</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18931</t>
+          <t>18384</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1873</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10077</t>
+          <t>9970</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7170</t>
+          <t>7058</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>25007</t>
+          <t>23452</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>643857</t>
+          <t>644404</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>658714</t>
+          <t>658748</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>683776</t>
+          <t>683883</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>691980</t>
+          <t>692784</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1331634</t>
+          <t>1333189</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1349471</t>
+          <t>1349583</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2065</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11554</t>
+          <t>12453</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10538</t>
+          <t>10995</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5237</t>
+          <t>4335</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17796</t>
+          <t>18115</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>767544</t>
+          <t>766645</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>777055</t>
+          <t>777033</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>812040</t>
+          <t>811583</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>821549</t>
+          <t>821446</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1583880</t>
+          <t>1583561</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1596439</t>
+          <t>1597341</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -3475,12 +3475,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>15559</t>
+          <t>15755</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>37453</t>
+          <t>38256</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3490,12 +3490,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>13881</t>
+          <t>14702</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>32609</t>
+          <t>33293</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3525,12 +3525,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>33844</t>
+          <t>34241</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>63330</t>
+          <t>63142</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3560,12 +3560,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -3588,12 +3588,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3389326</t>
+          <t>3388523</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3411220</t>
+          <t>3411024</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3603,12 +3603,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3522489</t>
+          <t>3521805</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3541217</t>
+          <t>3540396</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6918547</t>
+          <t>6918735</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6948033</t>
+          <t>6947636</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>1723</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13498</t>
+          <t>12260</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4618</t>
+          <t>5498</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12953</t>
+          <t>13247</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>280263</t>
+          <t>281501</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>292504</t>
+          <t>292038</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>284085</t>
+          <t>283205</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>569511</t>
+          <t>569217</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>580585</t>
+          <t>580660</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,69%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8658</t>
+          <t>10601</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8055</t>
+          <t>7723</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11682</t>
+          <t>12296</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>493917</t>
+          <t>491974</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>501558</t>
+          <t>501562</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>515029</t>
+          <t>515361</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1013977</t>
+          <t>1013363</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1023645</t>
+          <t>1023638</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4651</t>
+          <t>5196</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4477</t>
+          <t>4432</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5450</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>313914</t>
+          <t>313369</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>331832</t>
+          <t>331877</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>649424</t>
+          <t>648552</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6943</t>
+          <t>7450</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10432</t>
+          <t>10439</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>971</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13374</t>
+          <t>11365</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>363021</t>
+          <t>362514</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>376851</t>
+          <t>376844</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>743873</t>
+          <t>745882</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>756263</t>
+          <t>756276</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>6080</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6824</t>
+          <t>7102</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -5574,7 +5574,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>212588</t>
+          <t>212507</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>422984</t>
+          <t>422706</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8036</t>
+          <t>8308</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5809,7 +5809,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4502</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9687</t>
+          <t>9634</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -5882,7 +5882,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>255087</t>
+          <t>254815</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>268613</t>
+          <t>268459</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>526551</t>
+          <t>526604</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>535239</t>
+          <t>535224</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5967,7 +5967,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11588</t>
+          <t>11837</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6853</t>
+          <t>8207</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1123</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11850</t>
+          <t>11687</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -6225,7 +6225,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>644970</t>
+          <t>644721</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -6260,7 +6260,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>684441</t>
+          <t>683087</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1336002</t>
+          <t>1336165</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1346729</t>
+          <t>1346724</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3046</t>
+          <t>3728</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15978</t>
+          <t>17039</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>997</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8353</t>
+          <t>8363</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5234</t>
+          <t>5124</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19017</t>
+          <t>19033</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>762605</t>
+          <t>761544</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>775537</t>
+          <t>774855</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>817814</t>
+          <t>817804</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>825171</t>
+          <t>825170</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1585733</t>
+          <t>1585717</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1599516</t>
+          <t>1599626</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6658,7 +6658,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,68%</t>
         </is>
       </c>
     </row>
@@ -6798,12 +6798,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>15005</t>
+          <t>15888</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>36242</t>
+          <t>37374</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7265</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>23697</t>
+          <t>24768</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6868,12 +6868,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>27544</t>
+          <t>27615</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>53748</t>
+          <t>55447</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -6911,12 +6911,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3358108</t>
+          <t>3356976</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3379345</t>
+          <t>3378462</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3520845</t>
+          <t>3519774</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3537277</t>
+          <t>3537350</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6885144</t>
+          <t>6883445</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6911348</t>
+          <t>6911277</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
